--- a/Data/ID_Generators/PORTUGAL_IDGenerator.xlsx
+++ b/Data/ID_Generators/PORTUGAL_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF493C79-676F-413D-865D-CAB9997C1087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ECAC18-933B-4858-8FB0-8DA652A3EF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="95">
   <si>
     <t>Country1</t>
   </si>
@@ -294,6 +294,33 @@
   </si>
   <si>
     <t>24982928 2AP36</t>
+  </si>
+  <si>
+    <t>24982928 2AP37</t>
+  </si>
+  <si>
+    <t>24982928 2AP38</t>
+  </si>
+  <si>
+    <t>24982928 2AP39</t>
+  </si>
+  <si>
+    <t>24982928 2AP40</t>
+  </si>
+  <si>
+    <t>24982928 2AP41</t>
+  </si>
+  <si>
+    <t>24982928 2AP42</t>
+  </si>
+  <si>
+    <t>24982928 2AP43</t>
+  </si>
+  <si>
+    <t>24982928 2AP44</t>
+  </si>
+  <si>
+    <t>24982928 2AP45</t>
   </si>
 </sst>
 </file>
@@ -695,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="15.33203125" customWidth="1"/>
@@ -3498,7 +3525,7 @@
         <v>31</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" ref="N67:N72" si="1">K67&amp;" "&amp;L67&amp;M67</f>
+        <f t="shared" ref="N67:N81" si="1">K67&amp;" "&amp;L67&amp;M67</f>
         <v>24982928 2AP31</v>
       </c>
     </row>
@@ -3710,6 +3737,804 @@
       <c r="N72" t="str">
         <f t="shared" si="1"/>
         <v>24982928 2AP36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="6">
+        <v>10000895679</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="6">
+        <v>100845879</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K73" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L73" t="s">
+        <v>44</v>
+      </c>
+      <c r="M73">
+        <v>37</v>
+      </c>
+      <c r="N73" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="6">
+        <v>10000895678</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="6">
+        <v>100845878</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K74" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L74" t="s">
+        <v>44</v>
+      </c>
+      <c r="M74">
+        <v>38</v>
+      </c>
+      <c r="N74" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="6">
+        <v>10000895677</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="6">
+        <v>100845877</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K75" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L75" t="s">
+        <v>44</v>
+      </c>
+      <c r="M75">
+        <v>39</v>
+      </c>
+      <c r="N75" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="6">
+        <v>10000895676</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="6">
+        <v>100845876</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K76" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L76" t="s">
+        <v>44</v>
+      </c>
+      <c r="M76">
+        <v>40</v>
+      </c>
+      <c r="N76" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="6">
+        <v>10000895675</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="6">
+        <v>100845875</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K77" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L77" t="s">
+        <v>44</v>
+      </c>
+      <c r="M77">
+        <v>41</v>
+      </c>
+      <c r="N77" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="6">
+        <v>10000895674</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="6">
+        <v>100845874</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="K78" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L78" t="s">
+        <v>44</v>
+      </c>
+      <c r="M78">
+        <v>42</v>
+      </c>
+      <c r="N78" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="6">
+        <v>10000895673</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="6">
+        <v>100845873</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K79" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L79" t="s">
+        <v>44</v>
+      </c>
+      <c r="M79">
+        <v>43</v>
+      </c>
+      <c r="N79" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="6">
+        <v>10000895672</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="6">
+        <v>100845872</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K80" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L80" t="s">
+        <v>44</v>
+      </c>
+      <c r="M80">
+        <v>44</v>
+      </c>
+      <c r="N80" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="6">
+        <v>10000895671</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="6">
+        <v>100845871</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K81" s="6">
+        <v>24982928</v>
+      </c>
+      <c r="L81" t="s">
+        <v>44</v>
+      </c>
+      <c r="M81">
+        <v>45</v>
+      </c>
+      <c r="N81" t="str">
+        <f t="shared" si="1"/>
+        <v>24982928 2AP45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
